--- a/csv/mon-nouns-countries.xlsx
+++ b/csv/mon-nouns-countries.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Win 11 Pro\Documents\GitHub\MonDictDB\csv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tumma\Documents\GitHub\WANCHAEM-25-01-06\MonDictDB\csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D68C1D7-44A5-4A0F-9C33-0A6BEB498172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846F131D-D4AE-422F-9B58-460F6ADE3D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12180" yWindow="0" windowWidth="16725" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="596">
   <si>
     <t>English short</t>
   </si>
@@ -796,9 +796,6 @@
     <t>the Republic of Korea</t>
   </si>
   <si>
-    <t>Republic of Moldova (the)</t>
-  </si>
-  <si>
     <t>the Republic of Moldova</t>
   </si>
   <si>
@@ -925,9 +922,6 @@
     <t>the Democratic Socialist Republic of Sri Lanka</t>
   </si>
   <si>
-    <t>Sudan (the)</t>
-  </si>
-  <si>
     <t>the Republic of the Sudan</t>
   </si>
   <si>
@@ -1018,24 +1012,15 @@
     <t>Ukraine</t>
   </si>
   <si>
-    <t>United Arab Emirates (the)</t>
-  </si>
-  <si>
     <t>the United Arab Emirates</t>
   </si>
   <si>
     <t>the United Kingdom of Great Britain and Northern Ireland</t>
   </si>
   <si>
-    <t>United Republic of Tanzania (the)</t>
-  </si>
-  <si>
     <t>the United Republic of Tanzania</t>
   </si>
   <si>
-    <t>United States of America (the)</t>
-  </si>
-  <si>
     <t>the United States of America</t>
   </si>
   <si>
@@ -1057,9 +1042,6 @@
     <t>the Republic of Vanuatu</t>
   </si>
   <si>
-    <t>Venezuela (Bolivarian Republic of)</t>
-  </si>
-  <si>
     <t>the Bolivarian Republic of Venezuela</t>
   </si>
   <si>
@@ -1087,9 +1069,6 @@
     <t>the Holy See *</t>
   </si>
   <si>
-    <t>State of Palestine (the) *</t>
-  </si>
-  <si>
     <t>the State of Palestine *</t>
   </si>
   <si>
@@ -1523,6 +1502,312 @@
   </si>
   <si>
     <t>ကၟိန်ဍုင် သမ္မတ သဵုယှေဝ်လေတ် ဒဳမဝ်ကရေတ်တေတ် သဳရိလင်္ကာ </t>
+  </si>
+  <si>
+    <t>ဗူဂေရဳယျာ </t>
+  </si>
+  <si>
+    <t>သမ္မတ ဍုင် ဗူဂေရဳယျာ</t>
+  </si>
+  <si>
+    <t>ရဝ်မေနဳယျာ</t>
+  </si>
+  <si>
+    <t>ဂျဝ်ဂျဳယျာ</t>
+  </si>
+  <si>
+    <t>အာဇာဗေဂျာန်</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် အာဇာဗေဂျာန်</t>
+  </si>
+  <si>
+    <t>အဖဂါန္နိသတာန်</t>
+  </si>
+  <si>
+    <t>ဍုင်စောဖါအေဿလာမ် အဖဂါန်န္နိသတာန်</t>
+  </si>
+  <si>
+    <t>အေဿလာမ် vs. အေတ်သလာမ်</t>
+  </si>
+  <si>
+    <t>အာဖရိက သၠုင်ကျာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ အာဖရိက သၠုင်ကျာ</t>
+  </si>
+  <si>
+    <t>သူဒါန်သၠုင်ကျာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ သူဒါန်သၠုင်ကျာ</t>
+  </si>
+  <si>
+    <t>အဳသဳအဝ်ပဳယျာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ဖေဝ်ဒရေဝ် ဒဳမဝ်ကရေတိတ် အဳသဳအဝ်ပဳယျာ</t>
+  </si>
+  <si>
+    <t>အာန်ဂဝ်လာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ အာန်ဂဝ်လာ</t>
+  </si>
+  <si>
+    <t>အာဂျေန်တဳနာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ အာဂျေန်တဳနာ</t>
+  </si>
+  <si>
+    <t>အာမေနဳယျာ</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် အာမေနဳယျာ</t>
+  </si>
+  <si>
+    <t>အဝ်သတြေလျာ</t>
+  </si>
+  <si>
+    <t>ဗါရေန်</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် ဨကရာဇ် ဗါရေန်</t>
+  </si>
+  <si>
+    <t>ဗရာဇြဳ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ဖေဝ်ဒရေဝ် ဗရာဇြဳ</t>
+  </si>
+  <si>
+    <t>ဘူရုန်ဒဳ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ဘူရုန်ဒဳ</t>
+  </si>
+  <si>
+    <t>ကနေဒါ</t>
+  </si>
+  <si>
+    <t>ကေမရူန်</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ကေမရူန်</t>
+  </si>
+  <si>
+    <t>ချာတ်</t>
+  </si>
+  <si>
+    <t>သမ္မတ ဍုၚ် ချာတ်</t>
+  </si>
+  <si>
+    <t>ကျူဗာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ကျူဗာ</t>
+  </si>
+  <si>
+    <t>ဖဳဂျဳ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ဖဳဂျဳ</t>
+  </si>
+  <si>
+    <t>ဂါမ္ဗဳယျ</t>
+  </si>
+  <si>
+    <t>သမတ ဂါမ္ဗဳယျာ</t>
+  </si>
+  <si>
+    <t>သမတ vs. သမ္မတ</t>
+  </si>
+  <si>
+    <t>ဂျဝ်ဒါန်</t>
+  </si>
+  <si>
+    <t>သၟိင်တၠဟတ်ရှီမိုက် ဂျဝ်ဒါန်</t>
+  </si>
+  <si>
+    <t>ကာဇြာတ်သတာန်</t>
+  </si>
+  <si>
+    <t>သမ္မတ ဍုင် ကာဇြာတ်သတာန်</t>
+  </si>
+  <si>
+    <t>ကေန်ညာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ကေန်ညာ</t>
+  </si>
+  <si>
+    <t>လေသဝ်ထဝ်</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် ဨကရာဇ် လေသဝ်ထဝ်</t>
+  </si>
+  <si>
+    <t>လဳဗျာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် လဳဗျာ</t>
+  </si>
+  <si>
+    <t>လဳတေန်သတာင်</t>
+  </si>
+  <si>
+    <t>ကၟိုန်ဍုင် သၟိင်တၠ လဳတေန်သ</t>
+  </si>
+  <si>
+    <t>မာလာဝဳ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ မာလာဝဳ</t>
+  </si>
+  <si>
+    <t>မဝ်ဒိုက်</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ မဝ်ဒိုက်</t>
+  </si>
+  <si>
+    <t xml:space="preserve">မာလဳ </t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ မာလဳ</t>
+  </si>
+  <si>
+    <t>မေတ်သဳကိုဝ်</t>
+  </si>
+  <si>
+    <t>ရးနိဂီု ပံင်ကောံ မေတ်သဳကိုဝ်</t>
+  </si>
+  <si>
+    <t>မောန်တဳနဳဂရဝ်</t>
+  </si>
+  <si>
+    <t>မဝ်ဇြာမ်ဗိက်</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ မဝ်ဇြာမ်ဗိက်</t>
+  </si>
+  <si>
+    <t>နာမဳဗဳယျ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ နာမဳဗဳယျာ</t>
+  </si>
+  <si>
+    <t>နယူဇြဳလာန်</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ဖေဝ်ဒရေဝ် နာင်ဂျဳရဳယျာ</t>
+  </si>
+  <si>
+    <t>နာင်ဂျဳရဳယျာ</t>
+  </si>
+  <si>
+    <t>နဳဂျေ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ နဳဂျေ</t>
+  </si>
+  <si>
+    <t>မက်သဳဒဝ်နဳယျာ သၟဝ်ကျာ</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် မက်သဳဒဝ်နဳယျာ သၟဝ်ကျာ</t>
+  </si>
+  <si>
+    <t>Moldova</t>
+  </si>
+  <si>
+    <t>မဝ်ဒဝ်ဗာ</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် မဝ်ဒဝ်ဗာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ရဝါန်ဒါ</t>
+  </si>
+  <si>
+    <t>ရဝါန်ဒါ</t>
+  </si>
+  <si>
+    <t>သေင်ကာပူ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ သေင်ကာပူ</t>
+  </si>
+  <si>
+    <t>သလဝ်ဗဳနဳယျာ</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် သလဝ်ဗဳနဳယျာ</t>
+  </si>
+  <si>
+    <t>သဝ်မာလဳယျာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ဖေဝ်ဒရေဝ် သဝ်မာလဳယျာ</t>
+  </si>
+  <si>
+    <t>Sudan</t>
+  </si>
+  <si>
+    <t>သူဒါန်</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ သူဒါန်</t>
+  </si>
+  <si>
+    <t>ယူဂါန်ဒါ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ယူဂါန်ဒါ</t>
+  </si>
+  <si>
+    <t>Tanzania</t>
+  </si>
+  <si>
+    <t>United Arab Emirates</t>
+  </si>
+  <si>
+    <t>တာန်ဇြာနဳယျာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ တာန်ဇြာနဳယျာ</t>
+  </si>
+  <si>
+    <t>United States of America</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင်ပံင်ကောံ အမေရိကာန်</t>
+  </si>
+  <si>
+    <t>ဥရုဂွေ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ဗၟံက် ဥရုဂွေ</t>
+  </si>
+  <si>
+    <t>Venezuela</t>
+  </si>
+  <si>
+    <t>ဇြာမ်ဗဳယျာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ဇြာမ်ဗဳယျာ</t>
+  </si>
+  <si>
+    <t>ဇြေမ်ဗာဗွေ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ဇြေမ်ဗာဗွေ</t>
+  </si>
+  <si>
+    <t>Palestine*</t>
   </si>
 </sst>
 </file>
@@ -1569,7 +1854,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1586,6 +1871,12 @@
         <fgColor rgb="FF008000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1599,7 +1890,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1613,6 +1904,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1948,11 +2243,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E204"/>
+  <dimension ref="A1:E205"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="40.85546875" style="2" customWidth="1"/>
     <col min="4" max="4" width="46.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" customWidth="1"/>
@@ -1963,24 +2258,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>500</v>
+      </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>501</v>
       </c>
       <c r="E2" s="6"/>
     </row>
@@ -1989,13 +2290,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="E3" s="6"/>
     </row>
@@ -2021,8 +2322,14 @@
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="B6" s="2" t="s">
+        <v>509</v>
+      </c>
       <c r="C6" s="2" t="s">
         <v>11</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>510</v>
       </c>
       <c r="E6" s="6"/>
     </row>
@@ -2039,8 +2346,14 @@
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="B8" s="2" t="s">
+        <v>511</v>
+      </c>
       <c r="C8" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>512</v>
       </c>
       <c r="E8" s="6"/>
     </row>
@@ -2048,8 +2361,14 @@
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="B9" s="2" t="s">
+        <v>513</v>
+      </c>
       <c r="C9" s="2" t="s">
         <v>16</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>514</v>
       </c>
       <c r="E9" s="6"/>
     </row>
@@ -2057,8 +2376,14 @@
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="B10" s="2" t="s">
+        <v>515</v>
+      </c>
       <c r="C10" s="2" t="s">
         <v>17</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>515</v>
       </c>
       <c r="E10" s="6"/>
     </row>
@@ -2067,13 +2392,13 @@
         <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E11" s="6"/>
     </row>
@@ -2081,8 +2406,14 @@
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="B12" s="2" t="s">
+        <v>498</v>
+      </c>
       <c r="C12" s="2" t="s">
         <v>21</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>499</v>
       </c>
       <c r="E12" s="6"/>
     </row>
@@ -2099,8 +2430,14 @@
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="B14" s="2" t="s">
+        <v>516</v>
+      </c>
       <c r="C14" s="2" t="s">
         <v>25</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>517</v>
       </c>
       <c r="E14" s="6"/>
     </row>
@@ -2109,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="E15" s="6"/>
     </row>
@@ -2133,13 +2470,13 @@
         <v>29</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E17" s="6"/>
     </row>
@@ -2148,13 +2485,13 @@
         <v>31</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="E18" s="6"/>
     </row>
@@ -2181,13 +2518,13 @@
         <v>36</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="E21" s="6"/>
     </row>
@@ -2202,16 +2539,16 @@
     </row>
     <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="E23" s="6"/>
     </row>
@@ -2228,23 +2565,29 @@
       <c r="A25" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="B25" s="2" t="s">
+        <v>518</v>
+      </c>
       <c r="C25" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="D25" s="2" t="s">
+        <v>519</v>
+      </c>
       <c r="E25" s="6"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="E26" s="6"/>
     </row>
@@ -2252,8 +2595,14 @@
       <c r="A27" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="B27" s="2" t="s">
+        <v>494</v>
+      </c>
       <c r="C27" s="2" t="s">
         <v>46</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>495</v>
       </c>
       <c r="E27" s="6"/>
     </row>
@@ -2279,8 +2628,14 @@
       <c r="A30" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="B30" s="2" t="s">
+        <v>520</v>
+      </c>
       <c r="C30" s="2" t="s">
         <v>51</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>521</v>
       </c>
       <c r="E30" s="6"/>
     </row>
@@ -2289,13 +2644,13 @@
         <v>52</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="E31" s="6"/>
     </row>
@@ -2303,8 +2658,14 @@
       <c r="A32" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="B32" s="2" t="s">
+        <v>523</v>
+      </c>
       <c r="C32" s="2" t="s">
         <v>55</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>524</v>
       </c>
       <c r="E32" s="6"/>
     </row>
@@ -2312,8 +2673,14 @@
       <c r="A33" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="B33" s="2" t="s">
+        <v>522</v>
+      </c>
       <c r="C33" s="2" t="s">
         <v>56</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>522</v>
       </c>
       <c r="E33" s="6"/>
     </row>
@@ -2330,8 +2697,14 @@
       <c r="A35" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="B35" s="2" t="s">
+        <v>525</v>
+      </c>
       <c r="C35" s="2" t="s">
         <v>60</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>526</v>
       </c>
       <c r="E35" s="6"/>
     </row>
@@ -2349,13 +2722,13 @@
         <v>63</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="E37" s="6"/>
     </row>
@@ -2409,13 +2782,13 @@
         <v>75</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="E43" s="6"/>
     </row>
@@ -2423,8 +2796,14 @@
       <c r="A44" s="2" t="s">
         <v>77</v>
       </c>
+      <c r="B44" s="2" t="s">
+        <v>527</v>
+      </c>
       <c r="C44" s="2" t="s">
         <v>78</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>528</v>
       </c>
       <c r="E44" s="6"/>
     </row>
@@ -2442,28 +2821,28 @@
         <v>81</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="E46" s="6"/>
     </row>
     <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>83</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="E47" s="6"/>
     </row>
@@ -2481,13 +2860,13 @@
         <v>86</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>87</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="E49" s="6"/>
     </row>
@@ -2532,13 +2911,13 @@
         <v>96</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="E54" s="6"/>
     </row>
@@ -2574,13 +2953,13 @@
         <v>104</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>105</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="E58" s="6"/>
     </row>
@@ -2597,8 +2976,14 @@
       <c r="A60" s="2" t="s">
         <v>108</v>
       </c>
+      <c r="B60" s="2" t="s">
+        <v>507</v>
+      </c>
       <c r="C60" s="2" t="s">
         <v>109</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>508</v>
       </c>
       <c r="E60" s="6"/>
     </row>
@@ -2606,8 +2991,14 @@
       <c r="A61" s="2" t="s">
         <v>110</v>
       </c>
+      <c r="B61" s="2" t="s">
+        <v>529</v>
+      </c>
       <c r="C61" s="2" t="s">
         <v>111</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>530</v>
       </c>
       <c r="E61" s="6"/>
     </row>
@@ -2616,13 +3007,13 @@
         <v>112</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>113</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="E62" s="6"/>
     </row>
@@ -2631,13 +3022,13 @@
         <v>114</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="E63" s="6"/>
     </row>
@@ -2654,8 +3045,14 @@
       <c r="A65" s="2" t="s">
         <v>118</v>
       </c>
+      <c r="B65" s="2" t="s">
+        <v>531</v>
+      </c>
       <c r="C65" s="2" t="s">
         <v>119</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>532</v>
       </c>
       <c r="E65" s="6"/>
     </row>
@@ -2663,8 +3060,14 @@
       <c r="A66" s="2" t="s">
         <v>120</v>
       </c>
+      <c r="B66" s="2" t="s">
+        <v>497</v>
+      </c>
       <c r="C66" s="2" t="s">
         <v>120</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>497</v>
       </c>
       <c r="E66" s="6"/>
     </row>
@@ -2673,13 +3076,13 @@
         <v>121</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>122</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="E67" s="6"/>
     </row>
@@ -2697,13 +3100,13 @@
         <v>125</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>126</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="E69" s="6"/>
     </row>
@@ -2775,13 +3178,13 @@
         <v>140</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>140</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="E77" s="6"/>
     </row>
@@ -2799,13 +3202,13 @@
         <v>142</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>143</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="E79" s="6"/>
     </row>
@@ -2814,13 +3217,13 @@
         <v>144</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>145</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="E80" s="6"/>
     </row>
@@ -2829,13 +3232,13 @@
         <v>146</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>147</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="E81" s="6"/>
     </row>
@@ -2844,13 +3247,13 @@
         <v>148</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>149</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="E82" s="6"/>
     </row>
@@ -2868,13 +3271,13 @@
         <v>151</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="E84" s="6"/>
     </row>
@@ -2883,13 +3286,13 @@
         <v>153</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>154</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="E85" s="6"/>
     </row>
@@ -2907,13 +3310,13 @@
         <v>156</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>156</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="E87" s="6"/>
     </row>
@@ -2921,8 +3324,14 @@
       <c r="A88" s="2" t="s">
         <v>157</v>
       </c>
+      <c r="B88" s="3" t="s">
+        <v>534</v>
+      </c>
       <c r="C88" s="2" t="s">
         <v>158</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>535</v>
       </c>
       <c r="E88" s="6"/>
     </row>
@@ -2930,8 +3339,14 @@
       <c r="A89" s="2" t="s">
         <v>159</v>
       </c>
+      <c r="B89" s="3" t="s">
+        <v>536</v>
+      </c>
       <c r="C89" s="2" t="s">
         <v>160</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>537</v>
       </c>
       <c r="E89" s="6"/>
     </row>
@@ -2939,8 +3354,14 @@
       <c r="A90" s="2" t="s">
         <v>161</v>
       </c>
+      <c r="B90" s="3" t="s">
+        <v>538</v>
+      </c>
       <c r="C90" s="2" t="s">
         <v>162</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>539</v>
       </c>
       <c r="E90" s="6"/>
     </row>
@@ -2958,13 +3379,13 @@
         <v>165</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>166</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="E92" s="6"/>
     </row>
@@ -2979,16 +3400,16 @@
     </row>
     <row r="94" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>169</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="E94" s="6"/>
     </row>
@@ -2997,13 +3418,13 @@
         <v>170</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>171</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="E95" s="6"/>
     </row>
@@ -3012,13 +3433,13 @@
         <v>172</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>173</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="E96" s="6"/>
     </row>
@@ -3026,8 +3447,14 @@
       <c r="A97" s="2" t="s">
         <v>174</v>
       </c>
+      <c r="B97" s="2" t="s">
+        <v>540</v>
+      </c>
       <c r="C97" s="2" t="s">
         <v>175</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>541</v>
       </c>
       <c r="E97" s="6"/>
     </row>
@@ -3044,8 +3471,14 @@
       <c r="A99" s="2" t="s">
         <v>178</v>
       </c>
+      <c r="B99" s="2" t="s">
+        <v>542</v>
+      </c>
       <c r="C99" s="2" t="s">
         <v>179</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>543</v>
       </c>
       <c r="E99" s="6"/>
     </row>
@@ -3053,8 +3486,14 @@
       <c r="A100" s="2" t="s">
         <v>180</v>
       </c>
+      <c r="B100" s="2" t="s">
+        <v>544</v>
+      </c>
       <c r="C100" s="2" t="s">
         <v>181</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>545</v>
       </c>
       <c r="E100" s="6"/>
     </row>
@@ -3063,13 +3502,13 @@
         <v>182</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>183</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="E101" s="6"/>
     </row>
@@ -3078,13 +3517,13 @@
         <v>184</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>185</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="E102" s="6"/>
     </row>
@@ -3101,8 +3540,14 @@
       <c r="A104" s="2" t="s">
         <v>188</v>
       </c>
+      <c r="B104" s="2" t="s">
+        <v>546</v>
+      </c>
       <c r="C104" s="2" t="s">
         <v>189</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>547</v>
       </c>
       <c r="E104" s="6"/>
     </row>
@@ -3111,13 +3556,13 @@
         <v>190</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>190</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="E105" s="6"/>
     </row>
@@ -3125,8 +3570,14 @@
       <c r="A106" s="2" t="s">
         <v>191</v>
       </c>
+      <c r="B106" s="2" t="s">
+        <v>548</v>
+      </c>
       <c r="C106" s="2" t="s">
         <v>192</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>549</v>
       </c>
       <c r="E106" s="6"/>
     </row>
@@ -3134,8 +3585,14 @@
       <c r="A107" s="2" t="s">
         <v>193</v>
       </c>
+      <c r="B107" s="2" t="s">
+        <v>550</v>
+      </c>
       <c r="C107" s="2" t="s">
         <v>194</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>551</v>
       </c>
       <c r="E107" s="6"/>
     </row>
@@ -3179,8 +3636,14 @@
       <c r="A112" s="2" t="s">
         <v>203</v>
       </c>
+      <c r="B112" s="2" t="s">
+        <v>552</v>
+      </c>
       <c r="C112" s="2" t="s">
         <v>204</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>553</v>
       </c>
       <c r="E112" s="6"/>
     </row>
@@ -3207,13 +3670,13 @@
         <v>209</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>209</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="E115" s="6"/>
     </row>
@@ -3221,8 +3684,14 @@
       <c r="A116" s="2" t="s">
         <v>210</v>
       </c>
+      <c r="B116" s="2" t="s">
+        <v>554</v>
+      </c>
       <c r="C116" s="2" t="s">
         <v>210</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>554</v>
       </c>
       <c r="E116" s="6"/>
     </row>
@@ -3239,8 +3708,14 @@
       <c r="A118" s="2" t="s">
         <v>213</v>
       </c>
+      <c r="B118" s="2" t="s">
+        <v>555</v>
+      </c>
       <c r="C118" s="2" t="s">
         <v>214</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>556</v>
       </c>
       <c r="E118" s="6"/>
     </row>
@@ -3257,8 +3732,14 @@
       <c r="A120" s="2" t="s">
         <v>217</v>
       </c>
+      <c r="B120" s="2" t="s">
+        <v>557</v>
+      </c>
       <c r="C120" s="2" t="s">
         <v>218</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>558</v>
       </c>
       <c r="E120" s="6"/>
     </row>
@@ -3276,13 +3757,13 @@
         <v>221</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="E122" s="6"/>
     </row>
@@ -3291,13 +3772,13 @@
         <v>222</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>223</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="E123" s="6"/>
     </row>
@@ -3305,8 +3786,14 @@
       <c r="A124" s="2" t="s">
         <v>224</v>
       </c>
+      <c r="B124" s="2" t="s">
+        <v>559</v>
+      </c>
       <c r="C124" s="2" t="s">
         <v>224</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>559</v>
       </c>
       <c r="E124" s="6"/>
     </row>
@@ -3323,8 +3810,14 @@
       <c r="A126" s="2" t="s">
         <v>227</v>
       </c>
+      <c r="B126" s="2" t="s">
+        <v>562</v>
+      </c>
       <c r="C126" s="2" t="s">
         <v>228</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>563</v>
       </c>
       <c r="E126" s="6"/>
     </row>
@@ -3332,8 +3825,14 @@
       <c r="A127" s="2" t="s">
         <v>229</v>
       </c>
+      <c r="B127" s="9" t="s">
+        <v>561</v>
+      </c>
       <c r="C127" s="2" t="s">
         <v>230</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>560</v>
       </c>
       <c r="E127" s="6"/>
     </row>
@@ -3341,8 +3840,14 @@
       <c r="A128" s="2" t="s">
         <v>231</v>
       </c>
+      <c r="B128" s="2" t="s">
+        <v>564</v>
+      </c>
       <c r="C128" s="2" t="s">
         <v>232</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>565</v>
       </c>
       <c r="E128" s="6"/>
     </row>
@@ -3351,13 +3856,13 @@
         <v>233</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>234</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="E129" s="6"/>
     </row>
@@ -3366,13 +3871,13 @@
         <v>235</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="E130" s="6"/>
     </row>
@@ -3381,13 +3886,13 @@
         <v>237</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>238</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="E131" s="6"/>
     </row>
@@ -3441,13 +3946,13 @@
         <v>249</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>250</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="E137" s="6"/>
     </row>
@@ -3456,13 +3961,13 @@
         <v>251</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>252</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="E138" s="6"/>
     </row>
@@ -3471,13 +3976,13 @@
         <v>253</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>254</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="E139" s="6"/>
     </row>
@@ -3492,664 +3997,763 @@
     </row>
     <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>257</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="E141" s="6"/>
     </row>
     <row r="142" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="C142" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C142" s="2" t="s">
-        <v>259</v>
+      <c r="D142" s="2" t="s">
+        <v>568</v>
       </c>
       <c r="E142" s="6"/>
     </row>
     <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>496</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>496</v>
       </c>
       <c r="E143" s="6"/>
     </row>
     <row r="144" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C144" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>262</v>
-      </c>
       <c r="D144" s="2" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="E144" s="6"/>
     </row>
     <row r="145" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C145" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C145" s="2" t="s">
-        <v>264</v>
+      <c r="D145" s="2" t="s">
+        <v>569</v>
       </c>
       <c r="E145" s="6"/>
     </row>
     <row r="146" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E146" s="6"/>
     </row>
     <row r="147" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E147" s="6"/>
     </row>
     <row r="148" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E148" s="6"/>
     </row>
     <row r="149" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="E149" s="6"/>
     </row>
     <row r="150" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="E150" s="6"/>
     </row>
     <row r="151" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="E151" s="6"/>
     </row>
     <row r="152" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B152" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>275</v>
-      </c>
       <c r="D152" s="2" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="E152" s="6"/>
     </row>
     <row r="153" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>277</v>
       </c>
       <c r="E153" s="6"/>
     </row>
     <row r="154" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B154" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>279</v>
-      </c>
       <c r="D154" s="2" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="E154" s="6"/>
     </row>
     <row r="155" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="E155" s="6"/>
     </row>
     <row r="156" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>283</v>
       </c>
       <c r="E156" s="6"/>
     </row>
     <row r="157" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C157" s="2" t="s">
-        <v>285</v>
+      <c r="D157" s="2" t="s">
+        <v>572</v>
       </c>
       <c r="E157" s="6"/>
     </row>
     <row r="158" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B158" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="D158" s="3" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="E158" s="6"/>
     </row>
     <row r="159" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C159" s="2" t="s">
-        <v>289</v>
+      <c r="D159" s="2" t="s">
+        <v>574</v>
       </c>
       <c r="E159" s="6"/>
     </row>
     <row r="160" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E160" s="6"/>
     </row>
     <row r="161" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C161" s="2" t="s">
-        <v>292</v>
+      <c r="D161" s="2" t="s">
+        <v>576</v>
       </c>
       <c r="E161" s="6"/>
     </row>
     <row r="162" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C162" s="2" t="s">
-        <v>294</v>
+      <c r="D162" s="2" t="s">
+        <v>504</v>
       </c>
       <c r="E162" s="6"/>
     </row>
     <row r="163" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C163" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C163" s="2" t="s">
-        <v>296</v>
+      <c r="D163" s="2" t="s">
+        <v>506</v>
       </c>
       <c r="E163" s="6"/>
     </row>
     <row r="164" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C164" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="B164" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>298</v>
-      </c>
       <c r="D164" s="3" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="E164" s="6"/>
     </row>
     <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B165" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C165" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="B165" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>300</v>
-      </c>
       <c r="D165" s="3" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="E165" s="6"/>
     </row>
     <row r="166" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>301</v>
+        <v>577</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>578</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>579</v>
       </c>
       <c r="E166" s="6"/>
     </row>
     <row r="167" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E167" s="6"/>
     </row>
     <row r="168" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="E168" s="6"/>
     </row>
     <row r="169" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="E169" s="6"/>
     </row>
     <row r="170" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="E170" s="6"/>
     </row>
     <row r="171" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E171" s="6"/>
     </row>
     <row r="172" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="E172" s="6"/>
     </row>
     <row r="173" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E174" s="6"/>
     </row>
     <row r="175" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E175" s="6"/>
     </row>
     <row r="176" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E176" s="6"/>
     </row>
     <row r="177" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E177" s="6"/>
     </row>
     <row r="178" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="E178" s="6"/>
     </row>
     <row r="179" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E179" s="6"/>
     </row>
     <row r="180" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E180" s="6"/>
     </row>
     <row r="181" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>580</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>581</v>
       </c>
       <c r="E181" s="6"/>
     </row>
     <row r="182" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="E182" s="6"/>
     </row>
     <row r="183" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>332</v>
+        <v>583</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="E183" s="6"/>
     </row>
     <row r="184" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="E184" s="6"/>
     </row>
     <row r="185" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>335</v>
+        <v>582</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>584</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>585</v>
       </c>
       <c r="E185" s="6"/>
     </row>
     <row r="186" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>337</v>
+        <v>586</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>587</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>587</v>
       </c>
       <c r="E186" s="6"/>
     </row>
     <row r="187" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>588</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>589</v>
       </c>
       <c r="E187" s="6"/>
     </row>
     <row r="188" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="E188" s="6"/>
     </row>
     <row r="189" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="E189" s="6"/>
     </row>
     <row r="190" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>345</v>
+        <v>590</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="E190" s="6"/>
     </row>
     <row r="191" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="E191" s="6"/>
     </row>
     <row r="192" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="E192" s="6"/>
     </row>
     <row r="193" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>349</v>
+        <v>343</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>591</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>350</v>
+        <v>344</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>592</v>
       </c>
       <c r="E193" s="6"/>
     </row>
     <row r="194" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>351</v>
+        <v>345</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>593</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>352</v>
+        <v>346</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>594</v>
       </c>
       <c r="E194" s="6"/>
     </row>
     <row r="195" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="E195" s="6"/>
     </row>
     <row r="196" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>355</v>
+        <v>595</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="E196" s="6"/>
     </row>
     <row r="197" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="E197" s="6"/>
     </row>
     <row r="198" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="E198" s="6"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>466</v>
+        <v>459</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B205" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>502</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/csv/mon-nouns-countries.xlsx
+++ b/csv/mon-nouns-countries.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tumma\Documents\GitHub\WANCHAEM-25-01-06\MonDictDB\csv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Win 11 Pro\Documents\GitHub\MonDictDB\csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846F131D-D4AE-422F-9B58-460F6ADE3D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033498E6-2AB5-4AC5-A35E-404B412D09F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="694">
   <si>
     <t>English short</t>
   </si>
@@ -136,9 +136,6 @@
     <t>the Kingdom of Bhutan</t>
   </si>
   <si>
-    <t>Bolivia (Plurinational State of)</t>
-  </si>
-  <si>
     <t>the Plurinational State of Bolivia</t>
   </si>
   <si>
@@ -298,9 +295,6 @@
     <t>the Commonwealth of Dominica</t>
   </si>
   <si>
-    <t>Dominican Republic (the)</t>
-  </si>
-  <si>
     <t>the Dominican Republic</t>
   </si>
   <si>
@@ -613,9 +607,6 @@
     <t>the Republic of Malta</t>
   </si>
   <si>
-    <t>Marshall Islands (the)</t>
-  </si>
-  <si>
     <t>the Republic of the Marshall Islands</t>
   </si>
   <si>
@@ -637,9 +628,6 @@
     <t>the United Mexican States</t>
   </si>
   <si>
-    <t>Micronesia (Federated States of)</t>
-  </si>
-  <si>
     <t>the Federated States of Micronesia</t>
   </si>
   <si>
@@ -1252,9 +1240,6 @@
     <t>အဳဂျပ်</t>
   </si>
   <si>
-    <t> သမ္မတအာရာပ် အဳဂျပ်</t>
-  </si>
-  <si>
     <t>သမ္မတအာရာပ် သူရိယ</t>
   </si>
   <si>
@@ -1507,9 +1492,6 @@
     <t>ဗူဂေရဳယျာ </t>
   </si>
   <si>
-    <t>သမ္မတ ဍုင် ဗူဂေရဳယျာ</t>
-  </si>
-  <si>
     <t>ရဝ်မေနဳယျာ</t>
   </si>
   <si>
@@ -1633,9 +1615,6 @@
     <t>ကာဇြာတ်သတာန်</t>
   </si>
   <si>
-    <t>သမ္မတ ဍုင် ကာဇြာတ်သတာန်</t>
-  </si>
-  <si>
     <t>ကေန်ညာ</t>
   </si>
   <si>
@@ -1808,6 +1787,321 @@
   </si>
   <si>
     <t>Palestine*</t>
+  </si>
+  <si>
+    <t>ဝေနေဇြုဲလာ</t>
+  </si>
+  <si>
+    <t>Bolivia</t>
+  </si>
+  <si>
+    <t>သမ္မတ ဗောလဳဗဳဝှာရ် ဍုင် ဝေနေဇြုဲလာ</t>
+  </si>
+  <si>
+    <t>ဝနဴတူ</t>
+  </si>
+  <si>
+    <t>ဥဇဗေကိသတာန်</t>
+  </si>
+  <si>
+    <t>တူဗာလူ</t>
+  </si>
+  <si>
+    <t>တာခ်မေနိသတာန်</t>
+  </si>
+  <si>
+    <t>တူနဳသဳယျာ</t>
+  </si>
+  <si>
+    <t>တြိနိဒဒ် ကဵု တောဗဂေါ</t>
+  </si>
+  <si>
+    <t>တောန်ဂါ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် ဨကရာဇ် တောန်ဂါ</t>
+  </si>
+  <si>
+    <t>တဝ်ဂဝ်</t>
+  </si>
+  <si>
+    <t>တာဂျဳကဳသတာန်</t>
+  </si>
+  <si>
+    <t>သူရဳနာမ်</t>
+  </si>
+  <si>
+    <t>တကအ် သဝ်လဝ်မန်</t>
+  </si>
+  <si>
+    <t>ဇြိအရာ လေအန်</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ဇြိအရာ လေအန်</t>
+  </si>
+  <si>
+    <t>သေရှေလ်</t>
+  </si>
+  <si>
+    <t>သေနေဂါလ်</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် ဗူဂေရဳယျာ</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် ကာဇြာတ်သတာန်</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် သေနေဂါလ်</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် သေရှေလ်</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် သူရဳနာမ်</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် တာဂျဳကဳသတာန်</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် တဝ်ဂဝ်</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် တြိနိဒဒ် ကဵု တောဗဂေါ</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် တူနဳသဳယျာ</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် ဥဇဗေကိသတာန်</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် ဝနဴတူ</t>
+  </si>
+  <si>
+    <t>သမာရဳနဝ်</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် သမာရဳနဝ်</t>
+  </si>
+  <si>
+    <t>သာမဝ်အာ</t>
+  </si>
+  <si>
+    <t>သင်လူသဳယျာ</t>
+  </si>
+  <si>
+    <t>ကာတာ</t>
+  </si>
+  <si>
+    <t>ရးနိဂီု ကာတာ</t>
+  </si>
+  <si>
+    <t>ရးနိဂီု တမၠး သာမဝ်အာ</t>
+  </si>
+  <si>
+    <t>ပေရူ</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် ပေရူ</t>
+  </si>
+  <si>
+    <t>ပရကွေ</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် ပရကွေ</t>
+  </si>
+  <si>
+    <t>ပပဴ နျူ ဂွါန်နေယ်</t>
+  </si>
+  <si>
+    <t>ရးနိဂီု တမၠး ပပဴ နျူ ဂွါန်နေယ်</t>
+  </si>
+  <si>
+    <t>ပနမာ</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် ပနမာ</t>
+  </si>
+  <si>
+    <t>ပလောဝ်</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် ပလောဝ်</t>
+  </si>
+  <si>
+    <t>နိကာရာဂွါ</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် နိကာရာဂွါ</t>
+  </si>
+  <si>
+    <t>နာအူရူ</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် နာအူရူ</t>
+  </si>
+  <si>
+    <t>မဝ်ရောက္ကဝ်</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် ဨကရာဇ် မဝ်ရောက္ကဝ်</t>
+  </si>
+  <si>
+    <t>မဝ်နာကဝ်</t>
+  </si>
+  <si>
+    <t>ကၟိုန်ဍုင် သၟိင်တၠ မဝ်နာကဝ်</t>
+  </si>
+  <si>
+    <t>Micronesia</t>
+  </si>
+  <si>
+    <t>မဝ်ရဳယှတ်</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ မဝ်ရဳယှတ်</t>
+  </si>
+  <si>
+    <t>မဴရိတနဳယျာ</t>
+  </si>
+  <si>
+    <t>သမ္မတအေတ်သလာမ် မဴရိတနဳယျာ</t>
+  </si>
+  <si>
+    <t>Marshall Islands</t>
+  </si>
+  <si>
+    <t>တကအ်မာရှေဝ်</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် တကအ်မာရှေဝ်</t>
+  </si>
+  <si>
+    <t>မာလ်တာ</t>
+  </si>
+  <si>
+    <t>သမ္မတဍုင် မာလ်တာ</t>
+  </si>
+  <si>
+    <t>တကအ် မက်ဒါဂါသကာ</t>
+  </si>
+  <si>
+    <t>သမ္မတ တကအ် မက်ဒါဂါသကာ</t>
+  </si>
+  <si>
+    <t>ဍုင်သမ္မတ လိဗေရဳယျာ</t>
+  </si>
+  <si>
+    <t>လိဗေရဳယျာ</t>
+  </si>
+  <si>
+    <t>ကာဂျစ္စတာန်</t>
+  </si>
+  <si>
+    <t>ဍုင်သမ္မတ ကာဂျသ်</t>
+  </si>
+  <si>
+    <t>ကဳရဳဗာတဳ</t>
+  </si>
+  <si>
+    <t>ဍုင်သမ္မတ ကဳရဳဗာတဳ</t>
+  </si>
+  <si>
+    <t>ဂျမေကာ</t>
+  </si>
+  <si>
+    <t>အာဲယျာလာန်</t>
+  </si>
+  <si>
+    <t>အာက်သလာန်</t>
+  </si>
+  <si>
+    <t>ဟောန်ဂျာရာသ်</t>
+  </si>
+  <si>
+    <t>ဍုင်သမ္မတ ဟောန်ဂျာရာသ်</t>
+  </si>
+  <si>
+    <t>ဟေတဳ</t>
+  </si>
+  <si>
+    <t>ဍုင်သမ္မတ ဟေတဳ</t>
+  </si>
+  <si>
+    <t>ဍုင်သမ္မတ ပံင်ကောံ ဂါဲယျာဏာ</t>
+  </si>
+  <si>
+    <t>ဂါဲယျာဏာ</t>
+  </si>
+  <si>
+    <t>ဂျဳနဳ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ဂျဳနဳ</t>
+  </si>
+  <si>
+    <t>ဂွါတဳမာလာ</t>
+  </si>
+  <si>
+    <t>ဍုင်သမ္မတ ဂွါတဳမာလာ</t>
+  </si>
+  <si>
+    <t>ဂြေန္နာဒါ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ဂြေန္နာဒါ </t>
+  </si>
+  <si>
+    <t>ဂါနာ</t>
+  </si>
+  <si>
+    <t>ဍုင်သမ္မတ ဂါနာ</t>
+  </si>
+  <si>
+    <t>ဂါဗောန်</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ဂါဗောန်</t>
+  </si>
+  <si>
+    <t>အေဿဝါတဳနဳ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် ဨကရာဇ် အေဿဝါတဳနဳ</t>
+  </si>
+  <si>
+    <t>အဳရဳထရဳယျာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် တွဵုရး အဳရဳထရဳယျာ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">တွဵုရး vs. ရးနိဂီု </t>
+  </si>
+  <si>
+    <t>ဂျဳနဳ အဳကွေတာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ဂျဳနဳ အဳကွေတာ</t>
+  </si>
+  <si>
+    <t>အလ် သလ်ဝဒေါရ်</t>
+  </si>
+  <si>
+    <t>ဍုင်သမ္မတ အလ် သလ်ဝဒေါရ်</t>
+  </si>
+  <si>
+    <t>ဨကွေဒေါရ်</t>
+  </si>
+  <si>
+    <t>သမ္မတအာရာပ် အဳဂျပ်</t>
+  </si>
+  <si>
+    <t>ဍုင်သမ္မတ ဨကွေဒေါရ်</t>
+  </si>
+  <si>
+    <t>Dominican Republic</t>
   </si>
 </sst>
 </file>
@@ -1854,7 +2148,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1877,6 +2171,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1890,7 +2202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1909,6 +2221,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2258,16 +2576,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -2275,13 +2593,13 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="E2" s="6"/>
     </row>
@@ -2290,13 +2608,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="E3" s="6"/>
     </row>
@@ -2323,13 +2641,13 @@
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="E6" s="6"/>
     </row>
@@ -2347,13 +2665,13 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="E8" s="6"/>
     </row>
@@ -2362,13 +2680,13 @@
         <v>15</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E9" s="6"/>
     </row>
@@ -2377,13 +2695,13 @@
         <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="E10" s="6"/>
     </row>
@@ -2392,13 +2710,13 @@
         <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E11" s="6"/>
     </row>
@@ -2407,13 +2725,13 @@
         <v>20</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="E12" s="6"/>
     </row>
@@ -2431,13 +2749,13 @@
         <v>24</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="E14" s="6"/>
     </row>
@@ -2446,13 +2764,13 @@
         <v>26</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E15" s="6"/>
     </row>
@@ -2470,13 +2788,13 @@
         <v>29</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="E17" s="6"/>
     </row>
@@ -2485,13 +2803,13 @@
         <v>31</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="E18" s="6"/>
     </row>
@@ -2518,2238 +2836,2564 @@
         <v>36</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E21" s="6"/>
     </row>
     <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="E22" s="6"/>
     </row>
     <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="E23" s="6"/>
     </row>
     <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="E24" s="6"/>
     </row>
     <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="E25" s="6"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E26" s="6"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>495</v>
+        <v>608</v>
       </c>
       <c r="E27" s="6"/>
     </row>
     <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E28" s="6"/>
     </row>
     <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="E29" s="6"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="E30" s="6"/>
     </row>
     <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E31" s="6"/>
     </row>
     <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="E32" s="6"/>
     </row>
     <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="E33" s="6"/>
     </row>
     <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="E34" s="6"/>
     </row>
     <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="E35" s="6"/>
     </row>
     <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E36" s="6"/>
     </row>
     <row r="37" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E37" s="6"/>
     </row>
     <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="E38" s="6"/>
     </row>
     <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="E39" s="6"/>
     </row>
     <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="E40" s="6"/>
     </row>
     <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="E41" s="6"/>
     </row>
     <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="E42" s="6"/>
     </row>
     <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="D43" s="3" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="E43" s="6"/>
     </row>
     <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="D44" s="2" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="E44" s="6"/>
     </row>
     <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="E45" s="6"/>
     </row>
     <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="D46" s="3" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="E46" s="6"/>
     </row>
     <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="E47" s="6"/>
     </row>
     <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="E48" s="6"/>
     </row>
     <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="D49" s="3" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="E49" s="6"/>
     </row>
     <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="E50" s="6"/>
     </row>
     <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="E51" s="6"/>
     </row>
     <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>92</v>
+        <v>693</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E52" s="6"/>
     </row>
     <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>690</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>692</v>
       </c>
       <c r="E53" s="6"/>
     </row>
     <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>410</v>
+        <v>691</v>
       </c>
       <c r="E54" s="6"/>
     </row>
     <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>688</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>689</v>
       </c>
       <c r="E55" s="6"/>
     </row>
     <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>686</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>687</v>
       </c>
       <c r="E56" s="6"/>
     </row>
     <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>683</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>684</v>
       </c>
       <c r="E57" s="6"/>
     </row>
     <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="E58" s="6"/>
     </row>
     <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>681</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>682</v>
       </c>
       <c r="E59" s="6"/>
     </row>
     <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="E60" s="6"/>
     </row>
     <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="E61" s="6"/>
     </row>
     <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="E62" s="6"/>
     </row>
     <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="E63" s="6"/>
     </row>
     <row r="64" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>679</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>680</v>
       </c>
       <c r="E64" s="6"/>
     </row>
     <row r="65" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="E65" s="6"/>
     </row>
     <row r="66" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="E66" s="6"/>
     </row>
     <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E67" s="6"/>
     </row>
     <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>677</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>678</v>
       </c>
       <c r="E68" s="6"/>
     </row>
     <row r="69" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E69" s="6"/>
     </row>
     <row r="70" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>675</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>676</v>
       </c>
       <c r="E70" s="6"/>
     </row>
     <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>673</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>674</v>
       </c>
       <c r="E71" s="6"/>
     </row>
     <row r="72" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>671</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>672</v>
       </c>
       <c r="E72" s="6"/>
     </row>
     <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>132</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="B73" s="11"/>
       <c r="C73" s="2" t="s">
-        <v>133</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="D73" s="11"/>
       <c r="E73" s="6"/>
     </row>
     <row r="74" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>670</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>669</v>
       </c>
       <c r="E74" s="6"/>
     </row>
     <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>667</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>668</v>
       </c>
       <c r="E75" s="6"/>
     </row>
     <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>665</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
+      </c>
+      <c r="D76" s="14" t="s">
+        <v>666</v>
       </c>
       <c r="E76" s="6"/>
     </row>
     <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="E77" s="6"/>
     </row>
     <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>664</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
+      </c>
+      <c r="D78" s="14" t="s">
+        <v>664</v>
       </c>
       <c r="E78" s="6"/>
     </row>
     <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E79" s="6"/>
     </row>
     <row r="80" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E80" s="6"/>
     </row>
     <row r="81" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E81" s="6"/>
     </row>
     <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="E82" s="6"/>
     </row>
     <row r="83" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>663</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>663</v>
       </c>
       <c r="E83" s="6"/>
     </row>
     <row r="84" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E84" s="6"/>
     </row>
     <row r="85" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="E85" s="6"/>
     </row>
     <row r="86" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>662</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>662</v>
       </c>
       <c r="E86" s="6"/>
     </row>
     <row r="87" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E87" s="6"/>
     </row>
     <row r="88" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="E88" s="6"/>
     </row>
     <row r="89" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>537</v>
+        <v>609</v>
       </c>
       <c r="E89" s="6"/>
     </row>
     <row r="90" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="E90" s="6"/>
     </row>
     <row r="91" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>660</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>661</v>
       </c>
       <c r="E91" s="6"/>
     </row>
     <row r="92" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E92" s="6"/>
     </row>
     <row r="93" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>658</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>659</v>
       </c>
       <c r="E93" s="6"/>
     </row>
     <row r="94" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E94" s="6"/>
     </row>
     <row r="95" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="E95" s="6"/>
     </row>
     <row r="96" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E96" s="6"/>
     </row>
     <row r="97" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="E97" s="6"/>
     </row>
     <row r="98" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>657</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>656</v>
       </c>
       <c r="E98" s="6"/>
     </row>
     <row r="99" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="E99" s="6"/>
     </row>
     <row r="100" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="E100" s="6"/>
     </row>
     <row r="101" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="E101" s="6"/>
     </row>
     <row r="102" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="E102" s="6"/>
     </row>
     <row r="103" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>654</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>655</v>
       </c>
       <c r="E103" s="6"/>
     </row>
     <row r="104" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="E104" s="6"/>
     </row>
     <row r="105" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E105" s="6"/>
     </row>
     <row r="106" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E106" s="6"/>
     </row>
     <row r="107" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="E107" s="6"/>
     </row>
     <row r="108" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>652</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>653</v>
       </c>
       <c r="E108" s="6"/>
     </row>
     <row r="109" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>197</v>
+        <v>649</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>650</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>651</v>
       </c>
       <c r="E109" s="6"/>
     </row>
     <row r="110" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>647</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
+      </c>
+      <c r="D110" s="10" t="s">
+        <v>648</v>
       </c>
       <c r="E110" s="6"/>
     </row>
     <row r="111" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>645</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>646</v>
       </c>
       <c r="E111" s="6"/>
     </row>
     <row r="112" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="E112" s="6"/>
     </row>
     <row r="113" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>205</v>
-      </c>
+        <v>644</v>
+      </c>
+      <c r="B113" s="11"/>
       <c r="C113" s="2" t="s">
-        <v>206</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="D113" s="11"/>
       <c r="E113" s="6"/>
     </row>
     <row r="114" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>642</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
+      </c>
+      <c r="D114" s="10" t="s">
+        <v>643</v>
       </c>
       <c r="E114" s="6"/>
     </row>
     <row r="115" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E115" s="6"/>
     </row>
     <row r="116" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="E116" s="6"/>
     </row>
     <row r="117" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>640</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
+      </c>
+      <c r="D117" s="8" t="s">
+        <v>641</v>
       </c>
       <c r="E117" s="6"/>
     </row>
     <row r="118" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="E118" s="6"/>
     </row>
     <row r="119" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>215</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="B119" s="11"/>
       <c r="C119" s="2" t="s">
-        <v>216</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="D119" s="11"/>
       <c r="E119" s="6"/>
     </row>
     <row r="120" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="E120" s="6"/>
     </row>
     <row r="121" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>638</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>639</v>
       </c>
       <c r="E121" s="6"/>
     </row>
     <row r="122" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="E122" s="6"/>
     </row>
     <row r="123" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="E123" s="6"/>
     </row>
     <row r="124" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="E124" s="6"/>
     </row>
     <row r="125" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>636</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>637</v>
       </c>
       <c r="E125" s="6"/>
     </row>
     <row r="126" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="E126" s="6"/>
     </row>
     <row r="127" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="E127" s="6"/>
     </row>
     <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="E128" s="6"/>
     </row>
     <row r="129" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="E129" s="6"/>
     </row>
     <row r="130" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="E130" s="6"/>
     </row>
     <row r="131" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E131" s="6"/>
     </row>
     <row r="132" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>634</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
+      </c>
+      <c r="D132" s="10" t="s">
+        <v>635</v>
       </c>
       <c r="E132" s="6"/>
     </row>
     <row r="133" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>632</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
+      </c>
+      <c r="D133" s="10" t="s">
+        <v>633</v>
       </c>
       <c r="E133" s="6"/>
     </row>
     <row r="134" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>630</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>631</v>
       </c>
       <c r="E134" s="6"/>
     </row>
     <row r="135" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>628</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>629</v>
       </c>
       <c r="E135" s="6"/>
     </row>
     <row r="136" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>626</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
+      </c>
+      <c r="D136" s="10" t="s">
+        <v>627</v>
       </c>
       <c r="E136" s="6"/>
     </row>
     <row r="137" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E137" s="6"/>
     </row>
     <row r="138" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="E138" s="6"/>
     </row>
     <row r="139" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="E139" s="6"/>
     </row>
     <row r="140" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>623</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
+      </c>
+      <c r="D140" s="10" t="s">
+        <v>624</v>
       </c>
       <c r="E140" s="6"/>
     </row>
     <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E141" s="6"/>
     </row>
     <row r="142" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="E142" s="6"/>
     </row>
     <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="E143" s="6"/>
     </row>
     <row r="144" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="E144" s="6"/>
     </row>
     <row r="145" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="E145" s="6"/>
     </row>
     <row r="146" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>264</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="B146" s="11"/>
       <c r="C146" s="2" t="s">
-        <v>264</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="D146" s="11"/>
       <c r="E146" s="6"/>
     </row>
     <row r="147" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>622</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>622</v>
       </c>
       <c r="E147" s="6"/>
     </row>
     <row r="148" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>266</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="B148" s="11"/>
       <c r="C148" s="2" t="s">
-        <v>266</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="D148" s="11"/>
       <c r="E148" s="6"/>
     </row>
     <row r="149" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>621</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>625</v>
       </c>
       <c r="E149" s="6"/>
     </row>
     <row r="150" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>619</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>620</v>
       </c>
       <c r="E150" s="6"/>
     </row>
     <row r="151" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>271</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="B151" s="11"/>
       <c r="C151" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E151" s="6"/>
     </row>
     <row r="152" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="E152" s="6"/>
     </row>
     <row r="153" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>607</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
+      </c>
+      <c r="D153" s="8" t="s">
+        <v>610</v>
       </c>
       <c r="E153" s="6"/>
     </row>
     <row r="154" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="E154" s="6"/>
     </row>
     <row r="155" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>606</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>611</v>
       </c>
       <c r="E155" s="6"/>
     </row>
     <row r="156" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
+      </c>
+      <c r="B156" s="8" t="s">
+        <v>604</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>605</v>
       </c>
       <c r="E156" s="6"/>
     </row>
     <row r="157" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="E157" s="6"/>
     </row>
     <row r="158" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E158" s="6"/>
     </row>
     <row r="159" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="E159" s="6"/>
     </row>
     <row r="160" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>603</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>603</v>
       </c>
       <c r="E160" s="6"/>
     </row>
     <row r="161" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="E161" s="6"/>
     </row>
     <row r="162" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="E162" s="6"/>
     </row>
     <row r="163" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E163" s="6"/>
     </row>
     <row r="164" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="E164" s="6"/>
     </row>
     <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="E165" s="6"/>
     </row>
     <row r="166" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="E166" s="6"/>
     </row>
     <row r="167" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
+      </c>
+      <c r="B167" s="8" t="s">
+        <v>602</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
+      </c>
+      <c r="D167" s="8" t="s">
+        <v>612</v>
       </c>
       <c r="E167" s="6"/>
     </row>
     <row r="168" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E168" s="6"/>
     </row>
     <row r="169" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="E169" s="6"/>
     </row>
     <row r="170" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E170" s="6"/>
     </row>
     <row r="171" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>601</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
+      </c>
+      <c r="D171" s="10" t="s">
+        <v>613</v>
       </c>
       <c r="E171" s="6"/>
     </row>
     <row r="172" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E172" s="6"/>
     </row>
     <row r="173" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>600</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>614</v>
       </c>
       <c r="E174" s="6"/>
     </row>
     <row r="175" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>598</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>599</v>
       </c>
       <c r="E175" s="6"/>
     </row>
     <row r="176" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>597</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
+      </c>
+      <c r="D176" s="10" t="s">
+        <v>615</v>
       </c>
       <c r="E176" s="6"/>
     </row>
     <row r="177" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>596</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
+      </c>
+      <c r="D177" s="8" t="s">
+        <v>616</v>
       </c>
       <c r="E177" s="6"/>
     </row>
     <row r="178" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E178" s="6"/>
     </row>
     <row r="179" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>595</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>595</v>
       </c>
       <c r="E179" s="6"/>
     </row>
     <row r="180" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>594</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>594</v>
       </c>
       <c r="E180" s="6"/>
     </row>
     <row r="181" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="E181" s="6"/>
     </row>
     <row r="182" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="E182" s="6"/>
     </row>
     <row r="183" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="E183" s="6"/>
     </row>
     <row r="184" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="E184" s="6"/>
     </row>
     <row r="185" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E185" s="6"/>
     </row>
     <row r="186" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="E186" s="6"/>
     </row>
     <row r="187" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="E187" s="6"/>
     </row>
     <row r="188" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>593</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
+      </c>
+      <c r="D188" s="8" t="s">
+        <v>617</v>
       </c>
       <c r="E188" s="6"/>
     </row>
     <row r="189" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>592</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
+      </c>
+      <c r="D189" s="10" t="s">
+        <v>618</v>
       </c>
       <c r="E189" s="6"/>
     </row>
     <row r="190" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>590</v>
+        <v>583</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>589</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
+      </c>
+      <c r="D190" s="8" t="s">
+        <v>591</v>
       </c>
       <c r="E190" s="6"/>
     </row>
     <row r="191" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="E191" s="6"/>
     </row>
     <row r="192" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E192" s="6"/>
     </row>
     <row r="193" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E193" s="6"/>
     </row>
     <row r="194" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="E194" s="6"/>
     </row>
     <row r="195" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E195" s="6"/>
     </row>
     <row r="196" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E196" s="6"/>
     </row>
     <row r="197" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E197" s="6"/>
     </row>
     <row r="198" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E198" s="6"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B205" s="2" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>502</v>
+        <v>496</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>685</v>
       </c>
     </row>
   </sheetData>

--- a/csv/mon-nouns-countries.xlsx
+++ b/csv/mon-nouns-countries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Win 11 Pro\Documents\GitHub\MonDictDB\csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033498E6-2AB5-4AC5-A35E-404B412D09F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B0DC96-49CE-4FEB-8FCE-38892F2AF63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="731">
   <si>
     <t>English short</t>
   </si>
@@ -88,9 +88,6 @@
     <t>the Republic of Azerbaijan</t>
   </si>
   <si>
-    <t>Bahamas (The)</t>
-  </si>
-  <si>
     <t>the Commonwealth of The Bahamas</t>
   </si>
   <si>
@@ -190,9 +187,6 @@
     <t>Canada</t>
   </si>
   <si>
-    <t>Central African Republic (the)</t>
-  </si>
-  <si>
     <t>the Central African Republic</t>
   </si>
   <si>
@@ -220,15 +214,9 @@
     <t>the Republic of Colombia</t>
   </si>
   <si>
-    <t>Comoros (the)</t>
-  </si>
-  <si>
     <t>the Union of the Comoros</t>
   </si>
   <si>
-    <t>Congo (the)</t>
-  </si>
-  <si>
     <t>the Republic of the Congo</t>
   </si>
   <si>
@@ -271,9 +259,6 @@
     <t>the Democratic People's Republic of Korea</t>
   </si>
   <si>
-    <t>Democratic Republic of the Congo (the)</t>
-  </si>
-  <si>
     <t>the Democratic Republic of the Congo</t>
   </si>
   <si>
@@ -2102,6 +2087,132 @@
   </si>
   <si>
     <t>Dominican Republic</t>
+  </si>
+  <si>
+    <t>ဒဝ်မဳနဳကေန်</t>
+  </si>
+  <si>
+    <t>ဍုင်သမ္မတ ဒဝ်မဳနဳကေန်</t>
+  </si>
+  <si>
+    <t>ဒဝ်မိနိခါ</t>
+  </si>
+  <si>
+    <t>Bahamas</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် တွဵုရးတအ် ဒဝ်မိနိခါ</t>
+  </si>
+  <si>
+    <t>ဗဟမာသ်</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် တွဵုရးတအ် ဗဟမာသ်</t>
+  </si>
+  <si>
+    <t>ဂျဳဘူတဳ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ဂျဳဘူတဳ</t>
+  </si>
+  <si>
+    <t>Democratic Republic of the Congo</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ဒဳမဝ်ကရေတိတ် ကောန်ဂဝ်</t>
+  </si>
+  <si>
+    <t>ကောန်ဂဝ် (DRC)</t>
+  </si>
+  <si>
+    <t>သာဲဗြုသ်</t>
+  </si>
+  <si>
+    <t>ဍုင်သမ္မတ သာဲဗြုသ်</t>
+  </si>
+  <si>
+    <t>ကဝ်တေအဳဝဝ်ရဳ</t>
+  </si>
+  <si>
+    <t>ဍုင်သမ္မတ ကဝ်တေအဳဝဝ်ရဳ</t>
+  </si>
+  <si>
+    <t>ကောသတာ ရဳကာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ကောသတာ ရဳကာ</t>
+  </si>
+  <si>
+    <t>Congo</t>
+  </si>
+  <si>
+    <t>ကောန်ဂဝ်-ဗရာဇြာဗဳလ်</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ကောန်ဂဝ်</t>
+  </si>
+  <si>
+    <t>Comoros</t>
+  </si>
+  <si>
+    <t>ကောလောမ်ဗဳယျာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ကောလောမ်ဗဳယျာ</t>
+  </si>
+  <si>
+    <t>ချဳလေ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ချဳလေ</t>
+  </si>
+  <si>
+    <t>အာဖရိက ဗဟဵု</t>
+  </si>
+  <si>
+    <t>Central African</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ အာဖရိက ဗဟဵု</t>
+  </si>
+  <si>
+    <t>ဗူကဳဏး သွာသဝ်</t>
+  </si>
+  <si>
+    <t>ဗဝ်သဝါနာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ဗဝ်သဝါနာ</t>
+  </si>
+  <si>
+    <t>ဗောလဳဗဳယျာ</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် တွဵုရး ကောန်ဂကူတအ် ဗောလဳဗဳယျာ</t>
+  </si>
+  <si>
+    <t>ဗေနိန်</t>
+  </si>
+  <si>
+    <t>ကၟိန်ဍုင် သမ္မတ ဗေနိန်</t>
+  </si>
+  <si>
+    <t>ဗေလိဇ်</t>
+  </si>
+  <si>
+    <t>ဗါဗေဒေါသ်</t>
+  </si>
+  <si>
+    <t>အာန်ဒဝ်ရာ</t>
+  </si>
+  <si>
+    <t>ကၟိုန်ဍုင် သၟိင်တၠ အာန်ဒဝ်ရာ</t>
+  </si>
+  <si>
+    <t>အာလ်ဂျေရဳယျာ</t>
+  </si>
+  <si>
+    <t>ဍုင်သမ္မတ ဒဳမဝ်ကရေတ္တေတ် ညးဍုင်ကွာန် အာလ်ဂျေရဳယျာ</t>
   </si>
 </sst>
 </file>
@@ -2564,10 +2675,10 @@
   <dimension ref="A1:E205"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="34.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.7109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="40.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="46.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="50" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2576,16 +2687,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -2593,13 +2704,13 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="E2" s="6"/>
     </row>
@@ -2608,13 +2719,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="E3" s="6"/>
     </row>
@@ -2622,8 +2733,14 @@
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="B4" s="2" t="s">
+        <v>729</v>
+      </c>
       <c r="C4" s="2" t="s">
         <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>730</v>
       </c>
       <c r="E4" s="6"/>
     </row>
@@ -2631,8 +2748,14 @@
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="B5" s="2" t="s">
+        <v>727</v>
+      </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>728</v>
       </c>
       <c r="E5" s="6"/>
     </row>
@@ -2641,13 +2764,13 @@
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="E6" s="6"/>
     </row>
@@ -2655,9 +2778,11 @@
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="B7" s="11"/>
       <c r="C7" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="D7" s="11"/>
       <c r="E7" s="6"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -2665,13 +2790,13 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="E8" s="6"/>
     </row>
@@ -2680,13 +2805,13 @@
         <v>15</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="E9" s="6"/>
     </row>
@@ -2695,13 +2820,13 @@
         <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="E10" s="6"/>
     </row>
@@ -2710,13 +2835,13 @@
         <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E11" s="6"/>
     </row>
@@ -2725,2675 +2850,2787 @@
         <v>20</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>23</v>
+      <c r="D13" s="10" t="s">
+        <v>695</v>
       </c>
       <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="D14" s="8" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E15" s="6"/>
     </row>
     <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>726</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>726</v>
       </c>
       <c r="E16" s="6"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E17" s="6"/>
     </row>
     <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="E18" s="6"/>
     </row>
     <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>725</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>725</v>
       </c>
       <c r="E19" s="6"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>35</v>
+      <c r="D20" s="8" t="s">
+        <v>724</v>
       </c>
       <c r="E20" s="6"/>
     </row>
     <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E21" s="6"/>
     </row>
     <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>590</v>
+        <v>585</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>721</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>722</v>
       </c>
       <c r="E22" s="6"/>
     </row>
     <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="E23" s="6"/>
     </row>
     <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>41</v>
+      <c r="D24" s="2" t="s">
+        <v>720</v>
       </c>
       <c r="E24" s="6"/>
     </row>
     <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="E25" s="6"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="E26" s="6"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="E27" s="6"/>
     </row>
     <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>718</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>718</v>
       </c>
       <c r="E28" s="6"/>
     </row>
     <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>48</v>
+      <c r="D29" s="2" t="s">
+        <v>510</v>
       </c>
       <c r="E29" s="6"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>515</v>
-      </c>
+      <c r="D30" s="11"/>
       <c r="E30" s="6"/>
     </row>
     <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E31" s="6"/>
     </row>
     <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E32" s="6"/>
     </row>
     <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="E33" s="6"/>
     </row>
     <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>56</v>
+        <v>716</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>715</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>717</v>
       </c>
       <c r="E34" s="6"/>
     </row>
     <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="E35" s="6"/>
     </row>
     <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>713</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>714</v>
       </c>
       <c r="E36" s="6"/>
     </row>
     <row r="37" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="E37" s="6"/>
     </row>
     <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>711</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>712</v>
       </c>
       <c r="E38" s="6"/>
     </row>
     <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>66</v>
-      </c>
+        <v>710</v>
+      </c>
+      <c r="B39" s="11"/>
       <c r="C39" s="2" t="s">
-        <v>67</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D39" s="11"/>
       <c r="E39" s="6"/>
     </row>
     <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>68</v>
+        <v>707</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>708</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>709</v>
       </c>
       <c r="E40" s="6"/>
     </row>
     <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>705</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>706</v>
       </c>
       <c r="E41" s="6"/>
     </row>
     <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>703</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>704</v>
       </c>
       <c r="E42" s="6"/>
     </row>
     <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="E43" s="6"/>
     </row>
     <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="E44" s="6"/>
     </row>
     <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>701</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>702</v>
       </c>
       <c r="E45" s="6"/>
     </row>
     <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="E46" s="6"/>
     </row>
     <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="E47" s="6"/>
     </row>
     <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>83</v>
+        <v>698</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>700</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>699</v>
       </c>
       <c r="E48" s="6"/>
     </row>
     <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="E49" s="6"/>
     </row>
     <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>696</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>697</v>
       </c>
       <c r="E50" s="6"/>
     </row>
     <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>691</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>693</v>
       </c>
       <c r="E51" s="6"/>
     </row>
     <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>693</v>
+        <v>688</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>689</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>690</v>
       </c>
       <c r="E52" s="6"/>
     </row>
     <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="E53" s="6"/>
     </row>
     <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="E54" s="6"/>
     </row>
     <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="E55" s="6"/>
     </row>
     <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="E56" s="6"/>
     </row>
     <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="E57" s="6"/>
     </row>
     <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="E58" s="6"/>
     </row>
     <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="E59" s="6"/>
     </row>
     <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="E60" s="6"/>
     </row>
     <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E61" s="6"/>
     </row>
     <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="E62" s="6"/>
     </row>
     <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E63" s="6"/>
     </row>
     <row r="64" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="E64" s="6"/>
     </row>
     <row r="65" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="E65" s="6"/>
     </row>
     <row r="66" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="E66" s="6"/>
     </row>
     <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="E67" s="6"/>
     </row>
     <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="E68" s="6"/>
     </row>
     <row r="69" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E69" s="6"/>
     </row>
     <row r="70" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="E70" s="6"/>
     </row>
     <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="E71" s="6"/>
     </row>
     <row r="72" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="E72" s="6"/>
     </row>
     <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B73" s="11"/>
       <c r="C73" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D73" s="11"/>
       <c r="E73" s="6"/>
     </row>
     <row r="74" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="E74" s="6"/>
     </row>
     <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="E75" s="6"/>
     </row>
     <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="E76" s="6"/>
     </row>
     <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="E77" s="6"/>
     </row>
     <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="E78" s="6"/>
     </row>
     <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="E79" s="6"/>
     </row>
     <row r="80" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E80" s="6"/>
     </row>
     <row r="81" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="E81" s="6"/>
     </row>
     <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="E82" s="6"/>
     </row>
     <row r="83" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="E83" s="6"/>
     </row>
     <row r="84" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="E84" s="6"/>
     </row>
     <row r="85" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="E85" s="6"/>
     </row>
     <row r="86" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E86" s="6"/>
     </row>
     <row r="87" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E87" s="6"/>
     </row>
     <row r="88" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="E88" s="6"/>
     </row>
     <row r="89" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="E89" s="6"/>
     </row>
     <row r="90" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="E90" s="6"/>
     </row>
     <row r="91" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E91" s="6"/>
     </row>
     <row r="92" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="E92" s="6"/>
     </row>
     <row r="93" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="E93" s="6"/>
     </row>
     <row r="94" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E94" s="6"/>
     </row>
     <row r="95" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E95" s="6"/>
     </row>
     <row r="96" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="E96" s="6"/>
     </row>
     <row r="97" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="E97" s="6"/>
     </row>
     <row r="98" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="E98" s="6"/>
     </row>
     <row r="99" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="E99" s="6"/>
     </row>
     <row r="100" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="E100" s="6"/>
     </row>
     <row r="101" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="E101" s="6"/>
     </row>
     <row r="102" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="E102" s="6"/>
     </row>
     <row r="103" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="E103" s="6"/>
     </row>
     <row r="104" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="E104" s="6"/>
     </row>
     <row r="105" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E105" s="6"/>
     </row>
     <row r="106" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="E106" s="6"/>
     </row>
     <row r="107" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E107" s="6"/>
     </row>
     <row r="108" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="E108" s="6"/>
     </row>
     <row r="109" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="E109" s="6"/>
     </row>
     <row r="110" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="E110" s="6"/>
     </row>
     <row r="111" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="E111" s="6"/>
     </row>
     <row r="112" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="E112" s="6"/>
     </row>
     <row r="113" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="B113" s="11"/>
       <c r="C113" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D113" s="11"/>
       <c r="E113" s="6"/>
     </row>
     <row r="114" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="E114" s="6"/>
     </row>
     <row r="115" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="E115" s="6"/>
     </row>
     <row r="116" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="E116" s="6"/>
     </row>
     <row r="117" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="E117" s="6"/>
     </row>
     <row r="118" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="E118" s="6"/>
     </row>
     <row r="119" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B119" s="11"/>
       <c r="C119" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D119" s="11"/>
       <c r="E119" s="6"/>
     </row>
     <row r="120" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="E120" s="6"/>
     </row>
     <row r="121" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E121" s="6"/>
     </row>
     <row r="122" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="E122" s="6"/>
     </row>
     <row r="123" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E123" s="6"/>
     </row>
     <row r="124" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="E124" s="6"/>
     </row>
     <row r="125" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="E125" s="6"/>
     </row>
     <row r="126" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="E126" s="6"/>
     </row>
     <row r="127" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="E127" s="6"/>
     </row>
     <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="E128" s="6"/>
     </row>
     <row r="129" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="E129" s="6"/>
     </row>
     <row r="130" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E130" s="6"/>
     </row>
     <row r="131" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="E131" s="6"/>
     </row>
     <row r="132" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="E132" s="6"/>
     </row>
     <row r="133" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="E133" s="6"/>
     </row>
     <row r="134" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D134" s="8" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="E134" s="6"/>
     </row>
     <row r="135" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="E135" s="6"/>
     </row>
     <row r="136" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D136" s="10" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="E136" s="6"/>
     </row>
     <row r="137" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E137" s="6"/>
     </row>
     <row r="138" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="E138" s="6"/>
     </row>
     <row r="139" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="E139" s="6"/>
     </row>
     <row r="140" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="E140" s="6"/>
     </row>
     <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="E141" s="6"/>
     </row>
     <row r="142" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="E142" s="6"/>
     </row>
     <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="E143" s="6"/>
     </row>
     <row r="144" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="E144" s="6"/>
     </row>
     <row r="145" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="E145" s="6"/>
     </row>
     <row r="146" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B146" s="11"/>
       <c r="C146" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D146" s="11"/>
       <c r="E146" s="6"/>
     </row>
     <row r="147" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="E147" s="6"/>
     </row>
     <row r="148" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B148" s="11"/>
       <c r="C148" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D148" s="11"/>
       <c r="E148" s="6"/>
     </row>
     <row r="149" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="E149" s="6"/>
     </row>
     <row r="150" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="E150" s="6"/>
     </row>
     <row r="151" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B151" s="11"/>
       <c r="C151" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E151" s="6"/>
     </row>
     <row r="152" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="E152" s="6"/>
     </row>
     <row r="153" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="E153" s="6"/>
     </row>
     <row r="154" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="E154" s="6"/>
     </row>
     <row r="155" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B155" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D155" s="2" t="s">
         <v>606</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>611</v>
       </c>
       <c r="E155" s="6"/>
     </row>
     <row r="156" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="E156" s="6"/>
     </row>
     <row r="157" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="E157" s="6"/>
     </row>
     <row r="158" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="E158" s="6"/>
     </row>
     <row r="159" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="E159" s="6"/>
     </row>
     <row r="160" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="E160" s="6"/>
     </row>
     <row r="161" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="E161" s="6"/>
     </row>
     <row r="162" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="E162" s="6"/>
     </row>
     <row r="163" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="E163" s="6"/>
     </row>
     <row r="164" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E164" s="6"/>
     </row>
     <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="E165" s="6"/>
     </row>
     <row r="166" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="E166" s="6"/>
     </row>
     <row r="167" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D167" s="8" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="E167" s="6"/>
     </row>
     <row r="168" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="E168" s="6"/>
     </row>
     <row r="169" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E169" s="6"/>
     </row>
     <row r="170" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E170" s="6"/>
     </row>
     <row r="171" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="D171" s="10" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="E171" s="6"/>
     </row>
     <row r="172" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="E172" s="6"/>
     </row>
     <row r="173" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="E174" s="6"/>
     </row>
     <row r="175" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="E175" s="6"/>
     </row>
     <row r="176" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D176" s="10" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="E176" s="6"/>
     </row>
     <row r="177" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="E177" s="6"/>
     </row>
     <row r="178" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="E178" s="6"/>
     </row>
     <row r="179" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="E179" s="6"/>
     </row>
     <row r="180" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="E180" s="6"/>
     </row>
     <row r="181" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="E181" s="6"/>
     </row>
     <row r="182" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="E182" s="6"/>
     </row>
     <row r="183" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="E183" s="6"/>
     </row>
     <row r="184" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="E184" s="6"/>
     </row>
     <row r="185" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E185" s="6"/>
     </row>
     <row r="186" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="E186" s="6"/>
     </row>
     <row r="187" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="E187" s="6"/>
     </row>
     <row r="188" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="D188" s="8" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E188" s="6"/>
     </row>
     <row r="189" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D189" s="10" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="E189" s="6"/>
     </row>
     <row r="190" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="E190" s="6"/>
     </row>
     <row r="191" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E191" s="6"/>
     </row>
     <row r="192" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E192" s="6"/>
     </row>
     <row r="193" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="E193" s="6"/>
     </row>
     <row r="194" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="E194" s="6"/>
     </row>
     <row r="195" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="E195" s="6"/>
     </row>
     <row r="196" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E196" s="6"/>
     </row>
     <row r="197" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E197" s="6"/>
     </row>
     <row r="198" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E198" s="6"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B205" s="2" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
   </sheetData>

--- a/csv/mon-nouns-countries.xlsx
+++ b/csv/mon-nouns-countries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tumma\Documents\GitHub\WANCHAEM-25-01-06\MonDictDB\csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3F233C-0BFC-4AD4-8432-A37458E9B0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8B9C18-C38D-49B7-8DB1-8C290E9D113C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="839">
   <si>
     <t>English short</t>
   </si>
@@ -2303,20 +2303,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">ဍုင်သမ္မတ ဒဳမဝ်ခြေတိတ် ညးဍုင်ကွာန် </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>အာလ်ဂျေရဳယာ</t>
-    </r>
-  </si>
-  <si>
     <t>အေဿလာမ် vs. အေတ်သလာမ် vs. အေဿလာံ</t>
   </si>
   <si>
@@ -2501,20 +2487,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">ဍုင်အေံမိရေတ် အေဿလာမ် </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>အဖဂါန္နိသတာန်</t>
-    </r>
-  </si>
-  <si>
     <t>ဗေလ်ဂျဳယေမ်</t>
   </si>
   <si>
@@ -2583,6 +2555,606 @@
     <t>ဗဿနဳယာ</t>
   </si>
   <si>
+    <t>ဗတ်သဝါနာ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဗတ်သဝါနာ</t>
+    </r>
+  </si>
+  <si>
+    <t>ဗြာဇြိလ်</t>
+  </si>
+  <si>
+    <t>သွေဒ္ဒရ်ရလ် vs ဖေဝ်ဒရေဝ်</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်ပံင်ကောံ သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဗြာဇြိလ်</t>
+    </r>
+  </si>
+  <si>
+    <t>ဂျာရ်မနဳ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်ပံင်ကောံ သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဂျာရ်မနဳ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဍုင်</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>အဿတြေလဳယာ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဍုင်</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဗါဗေဒေါသ်</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဍုင်</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဗေလိသ်</t>
+    </r>
+  </si>
+  <si>
+    <t>ဗြူနိုယ်</t>
+  </si>
+  <si>
+    <t>ဗုလ်ဂေရဳယာ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဗုလ်ဂေရဳယာ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>နေဂါရာ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ဗြူနိုယ် </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဒါရုဿလာမ်</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဘူရုန်ဒဳ</t>
+    </r>
+  </si>
+  <si>
+    <t>ကမ္ဗောဒဳယာ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ကၟိန်ဍုင်ဨကရာဇ် </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ကမ္ဗောဒဳယာ</t>
+    </r>
+  </si>
+  <si>
+    <t>ဂေမ္မရုန်</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဂေမ္မရုန်</t>
+    </r>
+  </si>
+  <si>
+    <t>ခါနာဒါ</t>
+  </si>
+  <si>
+    <r>
+      <t>ဍုင်</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ခါနာဒါ</t>
+    </r>
+  </si>
+  <si>
+    <t>အသွရိကာ ဗဟဵု</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>အသွရိကာ ဗဟဵု</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ချာတ်</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်အေံမိရေတ် အေဿလာမ် </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>အဖဂါနိဿတာန်</t>
+    </r>
+  </si>
+  <si>
+    <t>အဖဂါနိဿတာန်</t>
+  </si>
+  <si>
+    <t>ချိလေ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ချိလေ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ ညးဍုင်ကွာန် </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ကြုက်</t>
+    </r>
+  </si>
+  <si>
+    <t>ခေါလောမ်ဗဳယာ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ခေါလောမ်ဗဳယာ</t>
+    </r>
+  </si>
+  <si>
+    <t>ခံင်ဂေါ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ခံင်ဂေါ</t>
+    </r>
+  </si>
+  <si>
+    <t>ဗုရ်ကဳနာ သွာသောဝ်</t>
+  </si>
+  <si>
+    <r>
+      <t>ဍုင်</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဗုရ်ကဳနာ သွာသောဝ်</t>
+    </r>
+  </si>
+  <si>
+    <t>ခဿတာ ရိကာ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ခဿတာ ရိကာ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဍုင်သမ္မတ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ကဝ်တေအဳဝဝ်ရဳ</t>
+    </r>
+  </si>
+  <si>
+    <t>ဂြောဨရှဳယာ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဂြောဨရှဳယာ</t>
+    </r>
+  </si>
+  <si>
+    <t>ချူဗာ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ချူဗာ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>သာဲဗြုသ်</t>
+    </r>
+  </si>
+  <si>
+    <t>ချေက်ဂဳယာ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ချေက်</t>
+    </r>
+  </si>
+  <si>
+    <t>ကိုဝ်ရဳယာ သၟဝ်ကျာ </t>
+  </si>
+  <si>
+    <t>ကိုဝ်ရဳယာ သၠုင်ကျ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ကိုဝ်ရဳယာ သၠုင်ကျ</t>
+    </r>
+  </si>
+  <si>
+    <t>ဒေမ္မဝ်ခြေတိတ် vs ဒဳမဝ်ကရေတ္တေတ်</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ ဒေမ္မဝ်ခြေတိတ် ညးဍုင်ကွာန် </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>အာလ်ဂျေရဳယာ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ ဒေမ္မဝ်ခြေတိတ် ညးဍုင်ကွာန် </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ကိုဝ်ရဳယာ</t>
+    </r>
+  </si>
+  <si>
+    <t>ခံင်ဂေါ (ဒဳအာရ်သဳ)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ ဒေမ္မဝ်ခြေတိတ် </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ခံင်ဂေါ</t>
+    </r>
+  </si>
+  <si>
+    <t>ဒေန်မာတ်</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ကၟိန်ဍုင်ဨကရာဇ် </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဒေန်မာတ်</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဂျဳဘူတဳ</t>
+    </r>
+  </si>
+  <si>
+    <t>ဒေါမိနိကာ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်တွဵုရးတအ် </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဒေါမိနိကာ</t>
+    </r>
+  </si>
+  <si>
+    <t>ဒေါမိနိကေန်</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ဒေါမိနိကေန်</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ဍုင်</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -2604,7 +3176,7 @@
     </r>
   </si>
   <si>
-    <t>ဗတ်သဝါနာ</t>
+    <t>ဨကွာဒရ်</t>
   </si>
   <si>
     <r>
@@ -2617,18 +3189,15 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>ဗတ်သဝါနာ</t>
-    </r>
-  </si>
-  <si>
-    <t>ဗြာဇြိလ်</t>
-  </si>
-  <si>
-    <t>သွေဒ္ဒရ်ရလ် vs ဖေဝ်ဒရေဝ်</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">ဍုင်ပံင်ကောံ သမ္မတ </t>
+      <t>ဨကွာဒရ်</t>
+    </r>
+  </si>
+  <si>
+    <t>အဳဂျိပ်</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတအာရာပ် </t>
     </r>
     <r>
       <rPr>
@@ -2637,15 +3206,15 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>ဗြာဇြိလ်</t>
-    </r>
-  </si>
-  <si>
-    <t>ဂျာရ်မနဳ</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">ဍုင်ပံင်ကောံ သမ္မတ </t>
+      <t>အဳဂျိပ်</t>
+    </r>
+  </si>
+  <si>
+    <t>အေလ် သောဝဒရ်</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ဍုင်သမ္မတ </t>
     </r>
     <r>
       <rPr>
@@ -2654,7 +3223,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>ဂျာရ်မနဳ</t>
+      <t>အေလ် သောဝဒရ်</t>
     </r>
   </si>
 </sst>
@@ -3214,7 +3783,7 @@
         <v>486</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>486</v>
+        <v>797</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>728</v>
@@ -3223,7 +3792,7 @@
         <v>487</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3263,7 +3832,7 @@
         <v>726</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>749</v>
+        <v>821</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3303,7 +3872,7 @@
         <v>495</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3335,7 +3904,7 @@
         <v>497</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3355,7 +3924,7 @@
         <v>499</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3375,7 +3944,7 @@
         <v>500</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>738</v>
+        <v>779</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3395,7 +3964,7 @@
         <v>440</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3415,7 +3984,7 @@
         <v>485</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3435,7 +4004,7 @@
         <v>691</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3475,7 +4044,7 @@
         <v>382</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3495,7 +4064,7 @@
         <v>722</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>722</v>
+        <v>780</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3515,7 +4084,7 @@
         <v>445</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3526,7 +4095,7 @@
         <v>429</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>30</v>
@@ -3535,7 +4104,7 @@
         <v>430</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3546,7 +4115,7 @@
         <v>721</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>31</v>
@@ -3555,7 +4124,7 @@
         <v>721</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>768</v>
+        <v>781</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3575,7 +4144,7 @@
         <v>720</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3595,7 +4164,7 @@
         <v>387</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3606,7 +4175,7 @@
         <v>717</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>36</v>
@@ -3615,7 +4184,7 @@
         <v>718</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3626,7 +4195,7 @@
         <v>472</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>37</v>
@@ -3635,7 +4204,7 @@
         <v>473</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>774</v>
+        <v>832</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3646,7 +4215,7 @@
         <v>715</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>39</v>
@@ -3655,7 +4224,7 @@
         <v>716</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3666,7 +4235,7 @@
         <v>503</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>41</v>
@@ -3675,7 +4244,7 @@
         <v>504</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3685,8 +4254,8 @@
       <c r="B26" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>372</v>
+      <c r="C26" s="21" t="s">
+        <v>782</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>374</v>
@@ -3694,8 +4263,8 @@
       <c r="E26" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>373</v>
+      <c r="F26" s="21" t="s">
+        <v>785</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3705,8 +4274,8 @@
       <c r="B27" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>481</v>
+      <c r="C27" s="20" t="s">
+        <v>783</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>43</v>
@@ -3714,8 +4283,8 @@
       <c r="E27" s="6" t="s">
         <v>599</v>
       </c>
-      <c r="F27" s="6" t="s">
-        <v>599</v>
+      <c r="F27" s="18" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3725,8 +4294,8 @@
       <c r="B28" s="6" t="s">
         <v>714</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>714</v>
+      <c r="C28" s="20" t="s">
+        <v>805</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>44</v>
@@ -3734,8 +4303,8 @@
       <c r="E28" s="6" t="s">
         <v>714</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>714</v>
+      <c r="F28" s="18" t="s">
+        <v>806</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3745,7 +4314,7 @@
       <c r="B29" s="6" t="s">
         <v>505</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="20" t="s">
         <v>505</v>
       </c>
       <c r="D29" s="6" t="s">
@@ -3754,8 +4323,8 @@
       <c r="E29" s="6" t="s">
         <v>506</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>506</v>
+      <c r="F29" s="18" t="s">
+        <v>786</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3777,8 +4346,8 @@
       <c r="B31" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>353</v>
+      <c r="C31" s="20" t="s">
+        <v>787</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>50</v>
@@ -3786,8 +4355,8 @@
       <c r="E31" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>354</v>
+      <c r="F31" s="18" t="s">
+        <v>788</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3797,8 +4366,8 @@
       <c r="B32" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>508</v>
+      <c r="C32" s="20" t="s">
+        <v>789</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>52</v>
@@ -3806,8 +4375,8 @@
       <c r="E32" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>509</v>
+      <c r="F32" s="18" t="s">
+        <v>790</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3817,8 +4386,8 @@
       <c r="B33" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>507</v>
+      <c r="C33" s="20" t="s">
+        <v>791</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>53</v>
@@ -3826,8 +4395,8 @@
       <c r="E33" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="F33" s="6" t="s">
-        <v>507</v>
+      <c r="F33" s="18" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3837,8 +4406,8 @@
       <c r="B34" s="6" t="s">
         <v>711</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>711</v>
+      <c r="C34" s="20" t="s">
+        <v>793</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>54</v>
@@ -3846,8 +4415,8 @@
       <c r="E34" s="11" t="s">
         <v>713</v>
       </c>
-      <c r="F34" s="11" t="s">
-        <v>713</v>
+      <c r="F34" s="18" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3857,7 +4426,7 @@
       <c r="B35" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="20" t="s">
         <v>510</v>
       </c>
       <c r="D35" s="6" t="s">
@@ -3866,8 +4435,8 @@
       <c r="E35" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="F35" s="6" t="s">
-        <v>511</v>
+      <c r="F35" s="18" t="s">
+        <v>795</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3877,8 +4446,8 @@
       <c r="B36" s="6" t="s">
         <v>709</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>709</v>
+      <c r="C36" s="20" t="s">
+        <v>798</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>58</v>
@@ -3886,8 +4455,8 @@
       <c r="E36" s="11" t="s">
         <v>710</v>
       </c>
-      <c r="F36" s="11" t="s">
-        <v>710</v>
+      <c r="F36" s="18" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3897,7 +4466,7 @@
       <c r="B37" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="20" t="s">
         <v>349</v>
       </c>
       <c r="D37" s="6" t="s">
@@ -3906,8 +4475,8 @@
       <c r="E37" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>350</v>
+      <c r="F37" s="18" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3917,8 +4486,8 @@
       <c r="B38" s="6" t="s">
         <v>707</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>707</v>
+      <c r="C38" s="20" t="s">
+        <v>801</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>62</v>
@@ -3926,8 +4495,8 @@
       <c r="E38" s="11" t="s">
         <v>708</v>
       </c>
-      <c r="F38" s="11" t="s">
-        <v>708</v>
+      <c r="F38" s="18" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3949,8 +4518,8 @@
       <c r="B40" s="6" t="s">
         <v>704</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>704</v>
+      <c r="C40" s="20" t="s">
+        <v>803</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>64</v>
@@ -3958,8 +4527,8 @@
       <c r="E40" s="6" t="s">
         <v>705</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>705</v>
+      <c r="F40" s="18" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3969,8 +4538,8 @@
       <c r="B41" s="6" t="s">
         <v>701</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>701</v>
+      <c r="C41" s="20" t="s">
+        <v>807</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>66</v>
@@ -3978,8 +4547,8 @@
       <c r="E41" s="11" t="s">
         <v>702</v>
       </c>
-      <c r="F41" s="11" t="s">
-        <v>702</v>
+      <c r="F41" s="18" t="s">
+        <v>808</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3989,7 +4558,7 @@
       <c r="B42" s="6" t="s">
         <v>699</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="20" t="s">
         <v>699</v>
       </c>
       <c r="D42" s="6" t="s">
@@ -3998,8 +4567,8 @@
       <c r="E42" s="6" t="s">
         <v>700</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>700</v>
+      <c r="F42" s="20" t="s">
+        <v>809</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4009,8 +4578,8 @@
       <c r="B43" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="C43" s="7" t="s">
-        <v>470</v>
+      <c r="C43" s="21" t="s">
+        <v>810</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>70</v>
@@ -4018,8 +4587,8 @@
       <c r="E43" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="F43" s="7" t="s">
-        <v>478</v>
+      <c r="F43" s="19" t="s">
+        <v>811</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4029,8 +4598,8 @@
       <c r="B44" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>512</v>
+      <c r="C44" s="20" t="s">
+        <v>812</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>72</v>
@@ -4038,8 +4607,8 @@
       <c r="E44" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>513</v>
+      <c r="F44" s="18" t="s">
+        <v>813</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4049,7 +4618,7 @@
       <c r="B45" s="6" t="s">
         <v>697</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="20" t="s">
         <v>697</v>
       </c>
       <c r="D45" s="6" t="s">
@@ -4058,8 +4627,8 @@
       <c r="E45" s="11" t="s">
         <v>698</v>
       </c>
-      <c r="F45" s="11" t="s">
-        <v>698</v>
+      <c r="F45" s="18" t="s">
+        <v>814</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4069,8 +4638,8 @@
       <c r="B46" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="C46" s="7" t="s">
-        <v>465</v>
+      <c r="C46" s="21" t="s">
+        <v>815</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>76</v>
@@ -4078,8 +4647,8 @@
       <c r="E46" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="F46" s="7" t="s">
-        <v>466</v>
+      <c r="F46" s="19" t="s">
+        <v>816</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4089,8 +4658,8 @@
       <c r="B47" s="7" t="s">
         <v>479</v>
       </c>
-      <c r="C47" s="7" t="s">
-        <v>479</v>
+      <c r="C47" s="21" t="s">
+        <v>817</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>77</v>
@@ -4098,8 +4667,8 @@
       <c r="E47" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="F47" s="7" t="s">
-        <v>467</v>
+      <c r="F47" s="19" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4109,8 +4678,8 @@
       <c r="B48" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="C48" s="7" t="s">
-        <v>696</v>
+      <c r="C48" s="21" t="s">
+        <v>823</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>78</v>
@@ -4118,8 +4687,8 @@
       <c r="E48" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="F48" s="7" t="s">
-        <v>695</v>
+      <c r="F48" s="19" t="s">
+        <v>824</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4129,8 +4698,8 @@
       <c r="B49" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="C49" s="7" t="s">
-        <v>451</v>
+      <c r="C49" s="21" t="s">
+        <v>825</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>80</v>
@@ -4138,8 +4707,8 @@
       <c r="E49" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="F49" s="7" t="s">
-        <v>452</v>
+      <c r="F49" s="19" t="s">
+        <v>826</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4149,7 +4718,7 @@
       <c r="B50" s="7" t="s">
         <v>692</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="21" t="s">
         <v>692</v>
       </c>
       <c r="D50" s="6" t="s">
@@ -4158,8 +4727,8 @@
       <c r="E50" s="7" t="s">
         <v>693</v>
       </c>
-      <c r="F50" s="7" t="s">
-        <v>693</v>
+      <c r="F50" s="19" t="s">
+        <v>827</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4169,8 +4738,8 @@
       <c r="B51" s="7" t="s">
         <v>687</v>
       </c>
-      <c r="C51" s="7" t="s">
-        <v>687</v>
+      <c r="C51" s="21" t="s">
+        <v>828</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>84</v>
@@ -4178,8 +4747,8 @@
       <c r="E51" s="9" t="s">
         <v>689</v>
       </c>
-      <c r="F51" s="9" t="s">
-        <v>689</v>
+      <c r="F51" s="19" t="s">
+        <v>829</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4189,8 +4758,8 @@
       <c r="B52" s="6" t="s">
         <v>685</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>685</v>
+      <c r="C52" s="20" t="s">
+        <v>830</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>85</v>
@@ -4198,8 +4767,8 @@
       <c r="E52" s="11" t="s">
         <v>686</v>
       </c>
-      <c r="F52" s="11" t="s">
-        <v>686</v>
+      <c r="F52" s="18" t="s">
+        <v>831</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4209,8 +4778,8 @@
       <c r="B53" s="6" t="s">
         <v>681</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>681</v>
+      <c r="C53" s="20" t="s">
+        <v>833</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>87</v>
@@ -4218,8 +4787,8 @@
       <c r="E53" s="11" t="s">
         <v>683</v>
       </c>
-      <c r="F53" s="11" t="s">
-        <v>683</v>
+      <c r="F53" s="18" t="s">
+        <v>834</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4229,8 +4798,8 @@
       <c r="B54" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="C54" s="7" t="s">
-        <v>397</v>
+      <c r="C54" s="21" t="s">
+        <v>835</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>89</v>
@@ -4238,8 +4807,8 @@
       <c r="E54" s="6" t="s">
         <v>682</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>682</v>
+      <c r="F54" s="18" t="s">
+        <v>836</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4249,8 +4818,8 @@
       <c r="B55" s="7" t="s">
         <v>679</v>
       </c>
-      <c r="C55" s="7" t="s">
-        <v>679</v>
+      <c r="C55" s="21" t="s">
+        <v>837</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>91</v>
@@ -4258,8 +4827,8 @@
       <c r="E55" s="11" t="s">
         <v>680</v>
       </c>
-      <c r="F55" s="11" t="s">
-        <v>680</v>
+      <c r="F55" s="18" t="s">
+        <v>838</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4490,7 +5059,7 @@
         <v>435</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>114</v>
@@ -4499,7 +5068,7 @@
         <v>436</v>
       </c>
       <c r="F67" s="18" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -5726,7 +6295,7 @@
         <v>411</v>
       </c>
       <c r="C130" s="21" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>226</v>
@@ -5735,7 +6304,7 @@
         <v>412</v>
       </c>
       <c r="F130" s="20" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -5945,8 +6514,8 @@
       <c r="B141" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="C141" s="7" t="s">
-        <v>367</v>
+      <c r="C141" s="21" t="s">
+        <v>818</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>247</v>
@@ -5954,8 +6523,8 @@
       <c r="E141" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="F141" s="6" t="s">
-        <v>369</v>
+      <c r="F141" s="18" t="s">
+        <v>819</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -6781,7 +7350,7 @@
         <v>427</v>
       </c>
       <c r="C184" s="21" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D184" s="6" t="s">
         <v>321</v>
@@ -6790,7 +7359,7 @@
         <v>428</v>
       </c>
       <c r="F184" s="20" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="185" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -6821,7 +7390,7 @@
         <v>571</v>
       </c>
       <c r="C186" s="20" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D186" s="6" t="s">
         <v>323</v>
@@ -6830,7 +7399,7 @@
         <v>571</v>
       </c>
       <c r="F186" s="20" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="187" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -7067,7 +7636,7 @@
         <v>732</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E205" s="6" t="s">
         <v>676</v>
@@ -7080,8 +7649,11 @@
       <c r="B206" s="6" t="s">
         <v>733</v>
       </c>
+      <c r="C206" s="6" t="s">
+        <v>820</v>
+      </c>
       <c r="D206" s="6" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
     </row>
     <row r="209" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
